--- a/src/test/resource/Bulk_Upload_Awards_Template_local_success.xlsx
+++ b/src/test/resource/Bulk_Upload_Awards_Template_local_success.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\BEIS\source\transparency-db-publishing-subsidies-service\src\test\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D432F054-66BA-4654-B478-CEAD5C3B4145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB029DC1-44B0-4D72-9AFE-8C66014231EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1606,9 +1606,9 @@
     <col min="6" max="6" width="142.81640625" style="21" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="142.81640625" style="21" customWidth="1"/>
     <col min="8" max="8" width="93" style="21" customWidth="1"/>
-    <col min="9" max="9" width="27.7265625" style="21" customWidth="1"/>
-    <col min="10" max="10" width="61" style="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="61" style="21" customWidth="1"/>
+    <col min="9" max="9" width="61" style="21" customWidth="1"/>
+    <col min="10" max="10" width="27.7265625" style="21" customWidth="1"/>
+    <col min="11" max="11" width="61" style="21" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="66.26953125" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="37" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="54.7265625" style="21" bestFit="1" customWidth="1"/>
@@ -1652,14 +1652,14 @@
       <c r="H1" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="I1" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="J1" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="K1" s="36" t="s">
         <v>190</v>
-      </c>
-      <c r="K1" s="38" t="s">
-        <v>205</v>
       </c>
       <c r="L1" s="38" t="s">
         <v>204</v>
@@ -1727,11 +1727,11 @@
       <c r="H2" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="I2" s="24"/>
+      <c r="I2" s="24" t="s">
+        <v>206</v>
+      </c>
       <c r="J2" s="24"/>
-      <c r="K2" s="24" t="s">
-        <v>206</v>
-      </c>
+      <c r="K2" s="24"/>
       <c r="L2" s="24" t="s">
         <v>167</v>
       </c>
@@ -1799,13 +1799,13 @@
         <v>181</v>
       </c>
       <c r="I3" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="J3" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="K3" s="24" t="s">
         <v>192</v>
-      </c>
-      <c r="K3" s="24" t="s">
-        <v>206</v>
       </c>
       <c r="L3" s="24" t="s">
         <v>167</v>
@@ -14125,7 +14125,7 @@
           <x14:formula1>
             <xm:f>Dropdown!$H$2:$H$3</xm:f>
           </x14:formula1>
-          <xm:sqref>I4:L837 D4:D837 F4:G837</xm:sqref>
+          <xm:sqref>D4:D837 F4:G837 I4:K837 L4:L837</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1651CF2E-B307-4251-AA77-0C500A441B31}">
           <x14:formula1>
@@ -15328,50 +15328,55 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Government_x0020_Body xmlns="b413c3fd-5a3b-4239-b985-69032e371c04">BEIS</Government_x0020_Body>
-    <Date_x0020_Opened xmlns="b413c3fd-5a3b-4239-b985-69032e371c04">2020-09-02T20:32:49+00:00</Date_x0020_Opened>
-    <LegacyData xmlns="aaacb922-5235-4a66-b188-303b9b46fbd7" xsi:nil="true"/>
-    <Descriptor xmlns="0063f72e-ace3-48fb-9c1f-5b513408b31f" xsi:nil="true"/>
-    <TaxCatchAll xmlns="4ff8cd83-fc61-4182-af0d-9444b096b4cc">
-      <Value>1</Value>
-    </TaxCatchAll>
-    <Invision xmlns="58eecf05-07e6-460c-a17a-1e6913e0d7ae">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Invision>
-    <m975189f4ba442ecbf67d4147307b177 xmlns="4ff8cd83-fc61-4182-af0d-9444b096b4cc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">BEIS:Corporate Services:Digital Directorate:EU Exit, BRM and Assurance:EBRASS</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">10b60d33-9f3b-419c-b326-e542b5592571</TermId>
-        </TermInfo>
-      </Terms>
-    </m975189f4ba442ecbf67d4147307b177>
-    <Security_x0020_Classification xmlns="0063f72e-ace3-48fb-9c1f-5b513408b31f">OFFICIAL</Security_x0020_Classification>
-    <ijmz xmlns="58eecf05-07e6-460c-a17a-1e6913e0d7ae" xsi:nil="true"/>
-    <Retention_x0020_Label xmlns="a8f60570-4bd3-4f2b-950b-a996de8ab151" xsi:nil="true"/>
-    <Date_x0020_Closed xmlns="b413c3fd-5a3b-4239-b985-69032e371c04" xsi:nil="true"/>
-    <_dlc_DocId xmlns="4ff8cd83-fc61-4182-af0d-9444b096b4cc">E67A7M7FTMSZ-519618591-1208</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="4ff8cd83-fc61-4182-af0d-9444b096b4cc">
-      <Url>https://beisgov.sharepoint.com/sites/SCPTDbase/_layouts/15/DocIdRedir.aspx?ID=E67A7M7FTMSZ-519618591-1208</Url>
-      <Description>E67A7M7FTMSZ-519618591-1208</Description>
-    </_dlc_DocIdUrl>
-    <Invisiondesigns xmlns="58eecf05-07e6-460c-a17a-1e6913e0d7ae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095552673811A1544B9DC17E80367E3D9" ma:contentTypeVersion="23" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6c219bbdc66874a295362540fe1f1ca4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4ff8cd83-fc61-4182-af0d-9444b096b4cc" xmlns:ns3="0063f72e-ace3-48fb-9c1f-5b513408b31f" xmlns:ns4="b413c3fd-5a3b-4239-b985-69032e371c04" xmlns:ns5="a8f60570-4bd3-4f2b-950b-a996de8ab151" xmlns:ns6="aaacb922-5235-4a66-b188-303b9b46fbd7" xmlns:ns7="58eecf05-07e6-460c-a17a-1e6913e0d7ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea492d8f6df3c516113149b290687b47" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="" ns7:_="">
     <xsd:import namespace="4ff8cd83-fc61-4182-af0d-9444b096b4cc"/>
@@ -15739,86 +15744,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Government_x0020_Body xmlns="b413c3fd-5a3b-4239-b985-69032e371c04">BEIS</Government_x0020_Body>
+    <Date_x0020_Opened xmlns="b413c3fd-5a3b-4239-b985-69032e371c04">2020-09-02T20:32:49+00:00</Date_x0020_Opened>
+    <LegacyData xmlns="aaacb922-5235-4a66-b188-303b9b46fbd7" xsi:nil="true"/>
+    <Descriptor xmlns="0063f72e-ace3-48fb-9c1f-5b513408b31f" xsi:nil="true"/>
+    <TaxCatchAll xmlns="4ff8cd83-fc61-4182-af0d-9444b096b4cc">
+      <Value>1</Value>
+    </TaxCatchAll>
+    <Invision xmlns="58eecf05-07e6-460c-a17a-1e6913e0d7ae">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Invision>
+    <m975189f4ba442ecbf67d4147307b177 xmlns="4ff8cd83-fc61-4182-af0d-9444b096b4cc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">BEIS:Corporate Services:Digital Directorate:EU Exit, BRM and Assurance:EBRASS</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">10b60d33-9f3b-419c-b326-e542b5592571</TermId>
+        </TermInfo>
+      </Terms>
+    </m975189f4ba442ecbf67d4147307b177>
+    <Security_x0020_Classification xmlns="0063f72e-ace3-48fb-9c1f-5b513408b31f">OFFICIAL</Security_x0020_Classification>
+    <ijmz xmlns="58eecf05-07e6-460c-a17a-1e6913e0d7ae" xsi:nil="true"/>
+    <Retention_x0020_Label xmlns="a8f60570-4bd3-4f2b-950b-a996de8ab151" xsi:nil="true"/>
+    <Date_x0020_Closed xmlns="b413c3fd-5a3b-4239-b985-69032e371c04" xsi:nil="true"/>
+    <_dlc_DocId xmlns="4ff8cd83-fc61-4182-af0d-9444b096b4cc">E67A7M7FTMSZ-519618591-1208</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="4ff8cd83-fc61-4182-af0d-9444b096b4cc">
+      <Url>https://beisgov.sharepoint.com/sites/SCPTDbase/_layouts/15/DocIdRedir.aspx?ID=E67A7M7FTMSZ-519618591-1208</Url>
+      <Description>E67A7M7FTMSZ-519618591-1208</Description>
+    </_dlc_DocIdUrl>
+    <Invisiondesigns xmlns="58eecf05-07e6-460c-a17a-1e6913e0d7ae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6216EEDE-1870-4B1D-BF90-D3816A946FAF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AF44877-6D21-41C2-9736-04B57D725022}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBEDEBF5-0F8B-43D7-9E7F-E4CDAE2C086C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="b413c3fd-5a3b-4239-b985-69032e371c04"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="4ff8cd83-fc61-4182-af0d-9444b096b4cc"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a8f60570-4bd3-4f2b-950b-a996de8ab151"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="58eecf05-07e6-460c-a17a-1e6913e0d7ae"/>
-    <ds:schemaRef ds:uri="aaacb922-5235-4a66-b188-303b9b46fbd7"/>
-    <ds:schemaRef ds:uri="0063f72e-ace3-48fb-9c1f-5b513408b31f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB723818-A5CD-443A-A314-BAC9891A4BF8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15841,10 +15820,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBEDEBF5-0F8B-43D7-9E7F-E4CDAE2C086C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="b413c3fd-5a3b-4239-b985-69032e371c04"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="4ff8cd83-fc61-4182-af0d-9444b096b4cc"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a8f60570-4bd3-4f2b-950b-a996de8ab151"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="58eecf05-07e6-460c-a17a-1e6913e0d7ae"/>
+    <ds:schemaRef ds:uri="aaacb922-5235-4a66-b188-303b9b46fbd7"/>
+    <ds:schemaRef ds:uri="0063f72e-ace3-48fb-9c1f-5b513408b31f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AF44877-6D21-41C2-9736-04B57D725022}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6216EEDE-1870-4B1D-BF90-D3816A946FAF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
